--- a/Configs/GameConfig/Datas/expedition_event.xlsx
+++ b/Configs/GameConfig/Datas/expedition_event.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -49,10 +49,13 @@
     <t>option_id</t>
   </si>
   <si>
-    <t>effect</t>
-  </si>
-  <si>
-    <t>crystal_delta</t>
+    <t>*lst_effect</t>
+  </si>
+  <si>
+    <t>$type</t>
+  </si>
+  <si>
+    <t>money_delta</t>
   </si>
   <si>
     <t>exp_delta</t>
@@ -82,7 +85,16 @@
     <t>快速拆解出可回收晶体，但搬运时会造成碰撞损伤。</t>
   </si>
   <si>
-    <t>拆解补给箱，获得 60 晶体，全队失去 8 点生命。</t>
+    <t>add_money</t>
+  </si>
+  <si>
+    <t>获得 60 晶体。</t>
+  </si>
+  <si>
+    <t>add_player_marble_hp</t>
+  </si>
+  <si>
+    <t>全队失去 8 点生命</t>
   </si>
   <si>
     <t>整理战术笔记</t>
@@ -91,7 +103,10 @@
     <t>没有额外晶体，但每名 Marble 都能获得战前经验。</t>
   </si>
   <si>
-    <t>整理战术笔记，全队获得 12 点经验。</t>
+    <t>add_player_marble_exp</t>
+  </si>
+  <si>
+    <t>全队获得 12 点经验。</t>
   </si>
 </sst>
 </file>
@@ -477,7 +492,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -516,19 +531,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -661,7 +663,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -673,34 +675,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
@@ -785,7 +787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -804,6 +806,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -816,19 +821,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -837,22 +839,34 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1169,7 +1183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -1178,102 +1192,108 @@
     <col min="4" max="4" width="61.7272727272727" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.2727272727273" style="5" customWidth="1"/>
     <col min="6" max="6" width="14.6363636363636" style="5" customWidth="1"/>
-    <col min="7" max="7" width="54.6363636363636" style="5" customWidth="1"/>
-    <col min="8" max="8" width="16.4545454545455" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.5454545454545" style="5" customWidth="1"/>
-    <col min="10" max="10" width="10.3636363636364" style="5" customWidth="1"/>
-    <col min="11" max="11" width="53.8181818181818" style="5" customWidth="1"/>
-    <col min="12" max="14" width="9" style="5"/>
+    <col min="7" max="7" width="54.6363636363636" style="6" customWidth="1"/>
+    <col min="8" max="8" width="25.0909090909091" style="5" customWidth="1"/>
+    <col min="9" max="9" width="16.4545454545455" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.5454545454545" style="5" customWidth="1"/>
+    <col min="11" max="11" width="10.3636363636364" style="5" customWidth="1"/>
+    <col min="12" max="12" width="53.8181818181818" style="5" customWidth="1"/>
+    <col min="13" max="15" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:15">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
       <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:15">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
       <c r="K2" s="14"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:14">
-      <c r="A3" s="6" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:15">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="L3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:14">
+    <row r="4" s="2" customFormat="1" spans="1:15">
       <c r="A4" s="15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="G4" s="17"/>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
@@ -1281,145 +1301,160 @@
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:14">
-      <c r="A5" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
+    <row r="5" s="3" customFormat="1" spans="1:15">
+      <c r="A5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:14">
-      <c r="A6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
+    <row r="6" s="3" customFormat="1" spans="1:15">
+      <c r="A6" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:14">
-      <c r="A7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
+    <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:15">
+      <c r="A7" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
     </row>
-    <row r="8" customFormat="1" spans="1:14">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="21" t="s">
+    <row r="8" customFormat="1" spans="1:15">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="22">
+      <c r="C8" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="25">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="5">
+      <c r="G8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="5">
         <v>60</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5">
-        <v>-8</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="1:14">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="22">
-        <v>2</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5">
-        <v>12</v>
-      </c>
+    <row r="9" customFormat="1" spans="1:15">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="5"/>
+      <c r="K9" s="5">
+        <v>-8</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="1:14">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
+    <row r="10" customFormat="1" spans="1:15">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="E10" s="25">
+        <v>2</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="J10" s="5">
+        <v>12</v>
+      </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="L10" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
     </row>
-    <row r="11" customFormat="1" spans="1:14">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
+    <row r="11" customFormat="1" spans="1:15">
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="G11" s="6"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1427,15 +1462,16 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
     </row>
-    <row r="12" customFormat="1" spans="1:14">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
+    <row r="12" customFormat="1" spans="1:15">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -1443,15 +1479,16 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="1:14">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
+    <row r="13" customFormat="1" spans="1:15">
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
@@ -1459,11 +1496,29 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:15">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="H2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/expedition_event.xlsx
+++ b/Configs/GameConfig/Datas/expedition_event.xlsx
@@ -34,7 +34,7 @@
     <t>##var</t>
   </si>
   <si>
-    <t>event_id</t>
+    <t>event_config_id</t>
   </si>
   <si>
     <t>title</t>
@@ -787,7 +787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -824,14 +824,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -861,15 +855,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1183,11 +1168,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="16.4545454545455" style="5" customWidth="1"/>
+    <col min="2" max="2" width="18.9090909090909" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.2727272727273" style="5" customWidth="1"/>
     <col min="4" max="4" width="61.7272727272727" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.2727272727273" style="5" customWidth="1"/>
@@ -1224,154 +1209,154 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:15">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="12" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:15">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:15">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:15">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
     </row>
     <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:15">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
     </row>
     <row r="8" customFormat="1" spans="1:15">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="5">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -1396,11 +1381,11 @@
       <c r="O8" s="5"/>
     </row>
     <row r="9" customFormat="1" spans="1:15">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="6"/>
       <c r="H9" s="5" t="s">
@@ -1419,11 +1404,11 @@
       <c r="O9" s="5"/>
     </row>
     <row r="10" customFormat="1" spans="1:15">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="25">
+      <c r="E10" s="5">
         <v>2</v>
       </c>
       <c r="F10" s="5" t="s">
@@ -1446,74 +1431,6 @@
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
-    </row>
-    <row r="11" customFormat="1" spans="1:15">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" customFormat="1" spans="1:15">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:15">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:15">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Configs/GameConfig/Datas/expedition_event.xlsx
+++ b/Configs/GameConfig/Datas/expedition_event.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <t>##</t>
@@ -787,7 +793,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -831,9 +837,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1273,100 +1276,120 @@
       <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15"/>
+      <c r="B4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>13</v>
+      </c>
       <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="I4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:15">
-      <c r="A5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
+      <c r="A5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:15">
-      <c r="A6" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
+      <c r="A6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:15">
-      <c r="A7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
+      <c r="A7" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
     </row>
     <row r="8" customFormat="1" spans="1:15">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>15</v>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I8" s="5">
         <v>60</v>
@@ -1374,22 +1397,22 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
     </row>
     <row r="9" customFormat="1" spans="1:15">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="6"/>
       <c r="H9" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
@@ -1397,28 +1420,28 @@
         <v>-8</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
     </row>
     <row r="10" customFormat="1" spans="1:15">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5">
         <v>2</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
@@ -1426,7 +1449,7 @@
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>

--- a/Configs/GameConfig/Datas/expedition_event.xlsx
+++ b/Configs/GameConfig/Datas/expedition_event.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -1379,8 +1379,8 @@
       <c r="D8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5">
-        <v>1</v>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>18</v>
@@ -1431,8 +1431,8 @@
       <c r="B10" s="21"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="5">
-        <v>2</v>
+      <c r="E10" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>24</v>

--- a/Configs/GameConfig/Datas/expedition_event.xlsx
+++ b/Configs/GameConfig/Datas/expedition_event.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -113,6 +113,30 @@
   </si>
   <si>
     <t>全队获得 12 点经验。</t>
+  </si>
+  <si>
+    <t>森林泉水</t>
+  </si>
+  <si>
+    <t>遇到一滩泉水，如何处理呢？</t>
+  </si>
+  <si>
+    <t>喝水</t>
+  </si>
+  <si>
+    <t>回复全体士兵50点血量</t>
+  </si>
+  <si>
+    <t>全队回复 50 点生命</t>
+  </si>
+  <si>
+    <t>把钱丢进去看看</t>
+  </si>
+  <si>
+    <t>不知道为什么，你有种想要将所有钱都丢进去的冲动，似乎受到寓言故事的影响。</t>
+  </si>
+  <si>
+    <t>获得 1000 晶体</t>
   </si>
 </sst>
 </file>
@@ -1171,16 +1195,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
     <col min="2" max="2" width="18.9090909090909" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.2727272727273" style="5" customWidth="1"/>
     <col min="4" max="4" width="61.7272727272727" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.2727272727273" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14.6363636363636" style="5" customWidth="1"/>
-    <col min="7" max="7" width="54.6363636363636" style="6" customWidth="1"/>
+    <col min="5" max="6" width="17" style="5" customWidth="1"/>
+    <col min="7" max="7" width="85.1818181818182" style="6" customWidth="1"/>
     <col min="8" max="8" width="25.0909090909091" style="5" customWidth="1"/>
     <col min="9" max="9" width="16.4545454545455" style="5" customWidth="1"/>
     <col min="10" max="10" width="11.5454545454545" style="5" customWidth="1"/>
@@ -1454,6 +1477,65 @@
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5">
+        <v>50</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Configs/GameConfig/Datas/expedition_event.xlsx
+++ b/Configs/GameConfig/Datas/expedition_event.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -55,13 +55,16 @@
     <t>$type</t>
   </si>
   <si>
-    <t>money_delta</t>
-  </si>
-  <si>
-    <t>exp_delta</t>
-  </si>
-  <si>
-    <t>hp_delta</t>
+    <t>operation</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>hp</t>
   </si>
   <si>
     <t>summary</t>
@@ -73,7 +76,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>int</t>
+    <t>ExpeditionScaledValueConfig</t>
   </si>
   <si>
     <t>##</t>
@@ -94,13 +97,25 @@
     <t>add_money</t>
   </si>
   <si>
-    <t>获得 60 晶体。</t>
+    <t>add</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>获得 {money} 晶体。</t>
   </si>
   <si>
     <t>add_player_marble_hp</t>
   </si>
   <si>
-    <t>全队失去 8 点生命</t>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>tiny</t>
+  </si>
+  <si>
+    <t>全队失去 {hp} 点生命</t>
   </si>
   <si>
     <t>整理战术笔记</t>
@@ -112,7 +127,7 @@
     <t>add_player_marble_exp</t>
   </si>
   <si>
-    <t>全队获得 12 点经验。</t>
+    <t>全队获得 {exp} 点经验。</t>
   </si>
   <si>
     <t>森林泉水</t>
@@ -127,7 +142,7 @@
     <t>回复全体士兵50点血量</t>
   </si>
   <si>
-    <t>全队回复 50 点生命</t>
+    <t>全队回复 {hp} 点生命</t>
   </si>
   <si>
     <t>把钱丢进去看看</t>
@@ -136,7 +151,10 @@
     <t>不知道为什么，你有种想要将所有钱都丢进去的冲动，似乎受到寓言故事的影响。</t>
   </si>
   <si>
-    <t>获得 1000 晶体</t>
+    <t>large</t>
+  </si>
+  <si>
+    <t>获得 {money} 晶体</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1213,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -1205,14 +1223,15 @@
     <col min="5" max="6" width="17" style="5" customWidth="1"/>
     <col min="7" max="7" width="85.1818181818182" style="6" customWidth="1"/>
     <col min="8" max="8" width="25.0909090909091" style="5" customWidth="1"/>
-    <col min="9" max="9" width="16.4545454545455" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.5454545454545" style="5" customWidth="1"/>
-    <col min="11" max="11" width="10.3636363636364" style="5" customWidth="1"/>
-    <col min="12" max="12" width="53.8181818181818" style="5" customWidth="1"/>
-    <col min="13" max="15" width="9" style="5"/>
+    <col min="9" max="9" width="11.5454545454545" style="5" customWidth="1"/>
+    <col min="10" max="10" width="16.4545454545455" style="5" customWidth="1"/>
+    <col min="11" max="11" width="11.5454545454545" style="5" customWidth="1"/>
+    <col min="12" max="12" width="10.3636363636364" style="5" customWidth="1"/>
+    <col min="13" max="13" width="53.8181818181818" style="5" customWidth="1"/>
+    <col min="14" max="16" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" spans="1:16">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1235,11 +1254,12 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
-      <c r="M1" s="8"/>
+      <c r="M1" s="11"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:15">
+    <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1262,11 +1282,12 @@
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
-      <c r="M2" s="8"/>
+      <c r="M2" s="11"/>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:15">
+    <row r="3" s="1" customFormat="1" spans="1:16">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -1291,52 +1312,56 @@
       <c r="L3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="8"/>
+      <c r="M3" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:15">
+    <row r="4" s="2" customFormat="1" spans="1:16">
       <c r="A4" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="14"/>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="14"/>
+      <c r="J4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:15">
+    <row r="5" s="3" customFormat="1" spans="1:16">
       <c r="A5" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="16"/>
@@ -1352,10 +1377,11 @@
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:15">
+    <row r="6" s="3" customFormat="1" spans="1:16">
       <c r="A6" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="16"/>
@@ -1371,10 +1397,11 @@
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:15">
+    <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:16">
       <c r="A7" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="19"/>
@@ -1390,43 +1417,47 @@
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
       <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
     </row>
-    <row r="8" customFormat="1" spans="1:15">
+    <row r="8" customFormat="1" spans="1:16">
       <c r="A8" s="21"/>
       <c r="B8" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <v>60</v>
-      </c>
-      <c r="J8" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="1:15">
+    <row r="9" customFormat="1" spans="1:16">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -1435,112 +1466,118 @@
       <c r="F9" s="5"/>
       <c r="G9" s="6"/>
       <c r="H9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="5"/>
+        <v>25</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="J9" s="5"/>
-      <c r="K9" s="5">
-        <v>-8</v>
-      </c>
+      <c r="K9" s="5"/>
       <c r="L9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="1:15">
+    <row r="10" customFormat="1" spans="1:16">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="5">
-        <v>12</v>
-      </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="B11" s="21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5">
-        <v>50</v>
-      </c>
       <c r="L11" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <v>1000</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="B13" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="E1:M1"/>
+    <mergeCell ref="H2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/expedition_event.xlsx
+++ b/Configs/GameConfig/Datas/expedition_event.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -58,13 +58,22 @@
     <t>operation</t>
   </si>
   <si>
-    <t>money</t>
-  </si>
-  <si>
-    <t>exp</t>
-  </si>
-  <si>
-    <t>hp</t>
+    <t>tier</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>marble_count_tier</t>
+  </si>
+  <si>
+    <t>marble_count_value</t>
+  </si>
+  <si>
+    <t>marble_type_tier</t>
+  </si>
+  <si>
+    <t>marble_type_value</t>
   </si>
   <si>
     <t>summary</t>
@@ -76,7 +85,16 @@
     <t>string</t>
   </si>
   <si>
-    <t>ExpeditionScaledValueConfig</t>
+    <t>EnumOperation</t>
+  </si>
+  <si>
+    <t>EnumExpeditionRewardTier</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>MarbleSpawnConfig</t>
   </si>
   <si>
     <t>##</t>
@@ -1213,7 +1231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -1223,15 +1241,14 @@
     <col min="5" max="6" width="17" style="5" customWidth="1"/>
     <col min="7" max="7" width="85.1818181818182" style="6" customWidth="1"/>
     <col min="8" max="8" width="25.0909090909091" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.5454545454545" style="5" customWidth="1"/>
-    <col min="10" max="10" width="16.4545454545455" style="5" customWidth="1"/>
+    <col min="9" max="10" width="16.4545454545455" style="5" customWidth="1"/>
     <col min="11" max="11" width="11.5454545454545" style="5" customWidth="1"/>
-    <col min="12" max="12" width="10.3636363636364" style="5" customWidth="1"/>
-    <col min="13" max="13" width="53.8181818181818" style="5" customWidth="1"/>
-    <col min="14" max="16" width="9" style="5"/>
+    <col min="12" max="15" width="21.3636363636364" style="5" customWidth="1"/>
+    <col min="16" max="16" width="53.8181818181818" style="5" customWidth="1"/>
+    <col min="17" max="19" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" spans="1:19">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1255,11 +1272,14 @@
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:16">
+    <row r="2" s="1" customFormat="1" spans="1:19">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1283,11 +1303,14 @@
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:16">
+    <row r="3" s="1" customFormat="1" spans="1:19">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -1315,53 +1338,73 @@
       <c r="M3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
+      <c r="N3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:16">
+    <row r="4" s="2" customFormat="1" spans="1:19">
       <c r="A4" s="13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
+      <c r="I4" s="14" t="s">
+        <v>18</v>
+      </c>
       <c r="J4" s="14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
+        <v>20</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:16">
+    <row r="5" s="3" customFormat="1" spans="1:19">
       <c r="A5" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="16"/>
@@ -1378,10 +1421,13 @@
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
       <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:16">
+    <row r="6" s="3" customFormat="1" spans="1:19">
       <c r="A6" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="16"/>
@@ -1398,10 +1444,13 @@
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:16">
+    <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:19">
       <c r="A7" s="18" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="19"/>
@@ -1418,46 +1467,52 @@
       <c r="N7" s="19"/>
       <c r="O7" s="19"/>
       <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
     </row>
-    <row r="8" customFormat="1" spans="1:16">
+    <row r="8" customFormat="1" spans="1:19">
       <c r="A8" s="21"/>
       <c r="B8" s="21" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
-      <c r="M8" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
+      <c r="P8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="1:16">
+    <row r="9" customFormat="1" spans="1:19">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -1466,118 +1521,122 @@
       <c r="F9" s="5"/>
       <c r="G9" s="6"/>
       <c r="H9" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
+      <c r="P9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="1:16">
+    <row r="10" customFormat="1" spans="1:19">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="L10" s="5"/>
-      <c r="M10" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
+      <c r="P10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:19">
       <c r="B11" s="21" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:19">
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:19">
       <c r="B13" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E1:M1"/>
-    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="E1:P1"/>
+    <mergeCell ref="H2:P2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
